--- a/fixtures/xlsx/auto-filter/input.xlsx
+++ b/fixtures/xlsx/auto-filter/input.xlsx
@@ -10,10 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
+    <t>Product</t>
+  </si>
+  <si>
     <t>Price</t>
   </si>
   <si>
-    <t>Electronics</t>
+    <t>Tools</t>
   </si>
   <si>
     <t>Widget</t>
@@ -25,10 +28,7 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Tools</t>
+    <t>Electronics</t>
   </si>
 </sst>
 </file>
@@ -38,21 +38,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>9.99</v>
@@ -60,10 +60,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>29.99</v>

--- a/fixtures/xlsx/auto-filter/input.xlsx
+++ b/fixtures/xlsx/auto-filter/input.xlsx
@@ -10,25 +10,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Product</t>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Gadget</t>
   </si>
   <si>
     <t>Price</t>
   </si>
   <si>
-    <t>Tools</t>
+    <t>Product</t>
   </si>
   <si>
     <t>Widget</t>
   </si>
   <si>
-    <t>Gadget</t>
+    <t>Electronics</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Electronics</t>
+    <t>Tools</t>
   </si>
 </sst>
 </file>
@@ -38,21 +38,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>9.99</v>
@@ -60,10 +60,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>29.99</v>
